--- a/Result/profitability/2227.xlsx
+++ b/Result/profitability/2227.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.42375</v>
+        <v>0.1675</v>
       </c>
       <c r="N2" t="n">
-        <v>9.797499999999999</v>
+        <v>9.22625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4112499999999999</v>
+        <v>-0.04625000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>9.77375</v>
+        <v>9.3925</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.09249999999999996</v>
       </c>
       <c r="N4" t="n">
-        <v>9.97125</v>
+        <v>9.38625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.325</v>
+        <v>0.1799999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.938749999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.87</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.18625</v>
       </c>
       <c r="N6" t="n">
-        <v>9.346250000000001</v>
+        <v>8.987499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0.51625</v>
+        <v>0.11</v>
       </c>
       <c r="N7" t="n">
-        <v>9.215</v>
+        <v>8.705</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.3975</v>
       </c>
       <c r="N8" t="n">
-        <v>9.18</v>
+        <v>8.532499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.48125</v>
       </c>
       <c r="N9" t="n">
-        <v>9.216249999999999</v>
+        <v>9.21625</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3557</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3347</v>
+      </c>
+      <c r="E75" t="n">
+        <v>210</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-222</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-433</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-655</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-514</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1224999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.2525</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9213483146067416</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4675090252707581</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.109090909090909</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.389999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2882991556091675</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
